--- a/artfynd/A 45779-2024 artfynd.xlsx
+++ b/artfynd/A 45779-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150294</v>
       </c>
       <c r="B2" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121150295</v>
       </c>
       <c r="B3" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 45779-2024 artfynd.xlsx
+++ b/artfynd/A 45779-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150294</v>
+        <v>121150295</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>90727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150295</v>
+        <v>121150294</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>90709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 45779-2024 artfynd.xlsx
+++ b/artfynd/A 45779-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150295</v>
+        <v>121150294</v>
       </c>
       <c r="B2" t="n">
-        <v>90727</v>
+        <v>90710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150294</v>
+        <v>121150295</v>
       </c>
       <c r="B3" t="n">
-        <v>90709</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 45779-2024 artfynd.xlsx
+++ b/artfynd/A 45779-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150294</v>
+        <v>121150295</v>
       </c>
       <c r="B2" t="n">
-        <v>90710</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150295</v>
+        <v>121150294</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 45779-2024 artfynd.xlsx
+++ b/artfynd/A 45779-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150295</v>
+        <v>121150294</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>90713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150294</v>
+        <v>121150295</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>90731</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
